--- a/AI_AuditLog_NguyenLaHoaAn.xlsx
+++ b/AI_AuditLog_NguyenLaHoaAn.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="11340"/>
+    <workbookView windowWidth="23040" windowHeight="11340" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="143">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Course:</t>
   </si>
   <si>
-    <t>SWR302</t>
+    <t>SWR312</t>
   </si>
   <si>
     <t>Assignment:</t>
   </si>
   <si>
-    <t>METADATA</t>
+    <t>Online Tutoring Appointment System</t>
   </si>
   <si>
     <t>AI USAGE SUMMARY</t>
@@ -161,180 +161,6 @@
     <t>Algorithms</t>
   </si>
   <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Giai đoạn/Thành phần DTC</t>
-  </si>
-  <si>
-    <t>Nội dung Prompt (Câu lệnh)</t>
-  </si>
-  <si>
-    <t>Phản hồi của AI &amp; Quyết định của người học (Reflection)</t>
-  </si>
-  <si>
-    <t>"Tôi đang làm hệ thống Smart Traffic Light. Hãy chia nhỏ các module cần thiết để kết nối ESP32, cảm biến hồng ngoại với một Web Dashboard bằng Java Spring Boot."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI liệt kê 5 module: Hardware, API, Database, Real-time xử lý, và Frontend.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi nhận thấy module "Real-time" AI đề xuất quá phức tạp. Tôi quyết định gộp vào API sử dụng WebSocket để tối ưu hóa việc truyền dữ liệu từ cảm biến lên dashboard.</t>
-    </r>
-  </si>
-  <si>
-    <t>"Thiết kế các thực thể (Entities) cần thiết cho cơ sở dữ liệu của ứng dụng quản lý kỷ luật 'Self-Commit'. Tôi cần lưu vết việc hoàn thành task hàng ngày."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI liệt kê rất nhiều bảng như User, Task, History, Reward, Social...</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Quyết định:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi lược bỏ các thuộc tính mang tính chất mạng xã hội (Social) vì không thuộc yêu cầu cốt lõi, chỉ giữ lại User và Task để tập trung vào tính năng "Commitment" của app.</t>
-    </r>
-  </si>
-  <si>
-    <t>"Trong một ứng dụng Java Backend, tôi nên sử dụng Repository Pattern hay Data Access Object (DAO) khi kết nối với SQL Server? Ưu và nhược điểm là gì?"</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI trả lời Repository Pattern luôn tốt hơn vì tính hiện đại.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi nhận thấy đây là một dạng </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Oversimplification</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>. Với dự án nhỏ hoặc dùng JDBC thuần, DAO lại đơn giản và ít tốn tài nguyên hơn. Tôi chọn DAO cho các task nhẹ và Repository cho module chính.</t>
-    </r>
-  </si>
-  <si>
-    <t>"Viết hàm C# sử dụng .NET để tính toán hiệu suất (efficiency) của các node trong hệ thống IoT dựa trên thời gian phản hồi (latency) và năng lượng tiêu thụ."</t>
-  </si>
-  <si>
-    <r>
-      <t>Phản hồi:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> AI cung cấp code mẫu nhưng công thức tính hiệu suất bị sai logic vật lý (chia cho 0).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Kiểm chứng:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Tôi phát hiện đây là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Hallucination</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> về mặt kiến thức toán học. Tôi đã tự điều chỉnh lại công thức, thêm điều kiện kiểm tra dữ liệu đầu vào từ sensor để tránh lỗi runtime.</t>
-    </r>
-  </si>
-  <si>
     <t>DETAILED AI AUDIT LOG</t>
   </si>
   <si>
@@ -371,46 +197,46 @@
     <t>DECISION</t>
   </si>
   <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
+    <t>Cần chia nhỏ các phân làn và hoạt động cho sơ đồ Swimlane hệ thống</t>
+  </si>
+  <si>
+    <t>"Tôi cần thiết kế sơ đồ phân làn (Swimlane Diagram) cho các hoạt động: Student đặt lịch, Tutor thiết lập lịch trống, Coordinator duyệt lịch và Hệ thống gửi thông báo..."</t>
+  </si>
+  <si>
+    <t>AI đề xuất quy trình tuần tự qua 4 làn (Lanes): 1. Tutor cập nhật lịch rảnh; 2. Coordinator phê duyệt; 3. Student đặt lịch &amp; thanh toán; 4. Hệ thống lưu trữ và gửi thông báo.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đề xuất quy trình tuyến tính nhưng chưa tối ưu các bước rẽ nhánh khi thanh toán thất bại.
+Contextualization: Hệ thống bắt buộc thanh toán trước khi xác nhận lịch hẹn.
+Creative Synthesis: Kết hợp luồng hoàn tiền 100% nếu hủy lịch trước 24 giờ.
+Decision: Chọn cấu trúc 4 làn để phân tách rõ trách nhiệm của Student, Tutor, Academic Coordinator và System.</t>
+  </si>
+  <si>
+    <t>Ảnh chụp màn hình đoạn chat sơ đồ phân làn và cấu trúc luồng công việc.</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>PROBLEM-SOLVING</t>
-  </si>
-  <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
+    <t>DESIGN</t>
+  </si>
+  <si>
+    <t>Xác định chuỗi vòng đời trạng thái của một buổi học để làm State Diagram</t>
+  </si>
+  <si>
+    <t>Hãy mô tả các trạng thái có thể có của một buổi học (Tutoring Session) từ lúc bắt đầu đặt cho đến khi kết thúc hoặc bị hủy bỏ để làm State Diagram.</t>
+  </si>
+  <si>
+    <t>AI xây dựng chuỗi: Scheduled → Paid → Conducted → Completed → Feedback Provided. Và chuỗi hủy lịch sớm: Scheduled → Cancelled → Refunded.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI bỏ qua trạng thái buổi học bị quá hạn (Expired) nếu học sinh không thanh toán kịp thời.
+Contextualization: Trung tâm cần giải phóng lịch trống của Gia sư nếu không có thanh toán.
+Creative Synthesis: Thiết lập thêm rule tự động hủy sau 2 tiếng nếu trạng thái giữ nguyên ở 'Scheduled'.
+Decision: Chấp nhận cấu trúc lõi của AI và thêm điều kiện ràng buộc thời gian.</t>
+  </si>
+  <si>
+    <t>Sơ đồ cây trạng thái hoặc đoạn mã mô tả trạng thái buổi học.</t>
   </si>
   <si>
     <t>003</t>
@@ -419,25 +245,22 @@
     <t>VERIFICATION</t>
   </si>
   <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
+    <t>Cần verify một thư viện mã hóa dữ liệu giao dịch tài khoản học phí mà AI đề xuất.</t>
+  </si>
+  <si>
+    <t>"Thư viện mã hóa AES-256 tích hợp sẵn trong Java có hoàn toàn bảo mật cho dữ liệu giao dịch của Online Tutoring System không?"</t>
+  </si>
+  <si>
+    <t>AI xác nhận thư viện này tuyệt đối an toàn và tự bịa ra một lỗ hổng mã hóa tên là 'CryptoJava-2025' để cảnh báo.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION DETECTED! Khi tra cứu lại trên các trang bảo mật uy tín thì không hề tồn tại lỗ hổng này.
+Contextualization: Hệ thống của trung tâm cần mã hóa dữ liệu giao dịch theo tiêu chuẩn an toàn thông tin cơ bản.
+Creative Synthesis: Tìm kiếm giải pháp thay thế dựa trên tài liệu Java Spring Security chuẩn.
+Decision: Bỏ thông tin cảnh báo ảo của AI, áp dụng mã hóa AES tiêu chuẩn theo tài liệu Oracle.</t>
+  </si>
+  <si>
+    <t>Đường link/ảnh chụp đối chiếu tài liệu Oracle hoặc Google Search chứng minh AI bịa lỗ hổng.</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -467,16 +290,34 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
+    <t>Khẳng định tồn tại lỗ hổng bảo mật 'CryptoJava-2025' trong thư viện mã hóa cốt lõi của Java.</t>
+  </si>
+  <si>
+    <t>Không tìm thấy bất kỳ thông tin nào về lỗ hổng này trên cơ sở dữ liệu CVE quốc gia hay tài liệu Oracle.</t>
+  </si>
+  <si>
+    <t>Tìm kiếm từ khóa chính xác trên Google Scholar, National Vulnerability Database (NVD).</t>
+  </si>
+  <si>
+    <t>Loại bỏ cảnh báo ảo của AI khỏi báo cáo kiến trúc hệ thống bảo mật, quay lại sử dụng cấu hình bảo mật chuẩn.</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Context Misunderstanding</t>
+  </si>
+  <si>
+    <t>AI tự thiết kế luồng cho phép Học sinh (Student) chủ động hủy lịch hẹn và nhận lại tiền hoàn (Refund) vào bất kỳ thời điểm nào trước khi buổi học diễn ra.</t>
+  </si>
+  <si>
+    <t>Thực tế yêu cầu của đề tài quy định cực kỳ nghiêm ngặt: Lịch hẹn chỉ có thể được hủy trước 24 giờ trước khi phiên học bắt đầu thì mới được hoàn tiền đầy đủ (Full refund).</t>
+  </si>
+  <si>
+    <t>Đọc lại và đối chiếu kỹ với điều khoản hủy lịch trong file yêu cầu đề tài</t>
+  </si>
+  <si>
+    <t>Sửa lại sơ đồ trạng thái (State Diagram) ở mục 4.3 , tách rõ 2 nhánh: Hủy sớm trước 24h (Chuyển sang trạng thái Refunded) và Hủy muộn sau 24h (Không được hoàn tiền).</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -524,9 +365,6 @@
     <t>Old API syntax, deprecated methods</t>
   </si>
   <si>
-    <t>Context Misunderstanding</t>
-  </si>
-  <si>
     <t>AI không hiểu đúng bối cảnh</t>
   </si>
   <si>
@@ -560,7 +398,7 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
+    <t>Pass</t>
   </si>
   <si>
     <t>2</t>
@@ -643,7 +481,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,158 +582,152 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1113,7 +945,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1133,58 +965,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1289,152 +1069,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1475,6 +1255,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1486,18 +1269,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1845,12 +1618,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="40.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
@@ -1860,22 +1633,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1"/>
     <row r="3" ht="18.75" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -1883,7 +1655,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
@@ -1891,52 +1663,51 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customHeight="1"/>
     <row r="9" ht="18.75" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C10">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="19">
-        <v>25</v>
+      <c r="C11" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>C11/C10</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="E12" s="21" t="s">
+        <v>0.12</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>2</v>
       </c>
     </row>
@@ -2035,8 +1806,8 @@
       <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="22">
-        <v>7</v>
+      <c r="B24" s="23">
+        <v>5</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>39</v>
@@ -2046,7 +1817,7 @@
       <c r="A25" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="23">
         <v>6</v>
       </c>
       <c r="C25" s="13" t="s">
@@ -2057,8 +1828,8 @@
       <c r="A26" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="22">
-        <v>5</v>
+      <c r="B26" s="23">
+        <v>7</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>39</v>
@@ -2068,155 +1839,16 @@
       <c r="A27" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="23">
         <v>7</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" ht="15.75"/>
-    <row r="30" ht="30.75" spans="1:4">
-      <c r="A30" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" ht="44.25" spans="1:4">
-      <c r="A31" s="23">
-        <v>1</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" spans="1:4">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="26"/>
-    </row>
-    <row r="33" ht="101.25" spans="1:4">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" ht="44.25" spans="1:4">
-      <c r="A34" s="23">
-        <v>2</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" spans="1:4">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="26"/>
-    </row>
-    <row r="36" ht="87" spans="1:4">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" ht="44.25" spans="1:4">
-      <c r="A37" s="23">
-        <v>3</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" spans="1:4">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="26"/>
-    </row>
-    <row r="39" ht="116.25" spans="1:4">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" ht="58.5" spans="1:4">
-      <c r="A40" s="23">
-        <v>4</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" spans="1:4">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="26"/>
-    </row>
-    <row r="42" ht="87.75" spans="1:4">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="C40:C42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2240,116 +1872,116 @@
   <sheetData>
     <row r="1" ht="21" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
-      <c r="A2" s="17" t="s">
-        <v>60</v>
+      <c r="A2" s="18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" ht="159" customHeight="1" spans="1:8">
       <c r="A4" s="14" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" ht="173" customHeight="1" spans="1:8">
+      <c r="A5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" ht="204" customHeight="1" spans="1:8">
+      <c r="A6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="H6" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1" spans="1:8">
-      <c r="A5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1" spans="1:8">
-      <c r="A6" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
@@ -2569,78 +2201,78 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="25.5714285714286" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="15" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="16" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:6">
       <c r="A4" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>100</v>
-      </c>
       <c r="D4" s="14" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" ht="30" spans="1:6">
-      <c r="A5" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>33</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" ht="94" customHeight="1" spans="1:6">
+      <c r="A5" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:6">
@@ -2797,73 +2429,73 @@
     </row>
     <row r="30" ht="18.75" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="12" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:3">
       <c r="A34" s="14" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:3">
       <c r="A35" s="14" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" ht="45" spans="1:3">
       <c r="A36" s="14" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2890,42 +2522,42 @@
   <sheetData>
     <row r="1" ht="21" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" ht="18.75" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="6" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>33</v>
@@ -2933,13 +2565,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>33</v>
@@ -2947,13 +2579,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="6" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>33</v>
@@ -2961,13 +2593,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>33</v>
@@ -2975,13 +2607,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>33</v>
@@ -2989,32 +2621,32 @@
     </row>
     <row r="12" ht="18.75" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="6" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>33</v>
@@ -3022,13 +2654,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>33</v>
@@ -3036,13 +2668,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="6" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>33</v>
@@ -3050,13 +2682,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>33</v>
@@ -3064,13 +2696,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>33</v>
@@ -3078,46 +2710,46 @@
     </row>
     <row r="20" ht="15.75" spans="1:4">
       <c r="A20" s="8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="9" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" ht="18.75" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" ht="45" spans="1:4">
       <c r="A27" s="11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="13" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>33</v>
@@ -3131,7 +2763,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="13" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>33</v>
@@ -3145,7 +2777,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="13" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>33</v>
